--- a/Training Plan_AWS DevOps (Cohort-1)_40 Hrs.xlsx
+++ b/Training Plan_AWS DevOps (Cohort-1)_40 Hrs.xlsx
@@ -1075,7 +1075,7 @@
       <c r="D6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="13"/>
@@ -1111,7 +1111,7 @@
       <c r="D8" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="12" t="s">
         <v>23</v>
       </c>
       <c r="F8" s="13"/>

--- a/Training Plan_AWS DevOps (Cohort-1)_40 Hrs.xlsx
+++ b/Training Plan_AWS DevOps (Cohort-1)_40 Hrs.xlsx
@@ -974,7 +974,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
@@ -1093,7 +1093,7 @@
       <c r="D7" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="12" t="s">
         <v>20</v>
       </c>
       <c r="F7" s="13"/>
@@ -1129,7 +1129,7 @@
       <c r="D9" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F9" s="13"/>
@@ -1199,6 +1199,9 @@
         <v>37</v>
       </c>
       <c r="F13" s="8"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/Training Plan_AWS DevOps (Cohort-1)_40 Hrs.xlsx
+++ b/Training Plan_AWS DevOps (Cohort-1)_40 Hrs.xlsx
@@ -1147,7 +1147,7 @@
       <c r="D10" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="12" t="s">
         <v>29</v>
       </c>
       <c r="F10" s="13"/>

--- a/Training Plan_AWS DevOps (Cohort-1)_40 Hrs.xlsx
+++ b/Training Plan_AWS DevOps (Cohort-1)_40 Hrs.xlsx
@@ -1165,7 +1165,7 @@
       <c r="D11" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="12" t="s">
         <v>32</v>
       </c>
       <c r="F11" s="13"/>
